--- a/Encollect_Web_DBS_P1/Cypress/fixtures/AgentTemplate.xlsx
+++ b/Encollect_Web_DBS_P1/Cypress/fixtures/AgentTemplate.xlsx
@@ -404,61 +404,61 @@
         <v>123456</v>
       </c>
       <c r="B2" t="str">
-        <v>Kovacek</v>
+        <v>Murray</v>
       </c>
       <c r="C2" t="str">
-        <v>AMNZVM</v>
+        <v>VSRSWK</v>
       </c>
       <c r="D2" t="str">
-        <v>Ulices95@yahoo.com</v>
+        <v>Ryan_Predovic@hotmail.com</v>
       </c>
       <c r="E2" t="str">
-        <v>JnfOKVSu</v>
+        <v>4vwvuMKz</v>
       </c>
       <c r="F2" t="str">
+        <v>2025-09-10</v>
+      </c>
+      <c r="G2" t="str">
+        <v>2025-06-27</v>
+      </c>
+      <c r="H2" t="str">
+        <v>FZpReDDzyW</v>
+      </c>
+      <c r="I2" t="str">
+        <v>Baby</v>
+      </c>
+      <c r="J2" t="str">
+        <v>Product Markets Consultant</v>
+      </c>
+      <c r="K2" t="str">
         <v>2025-03-10</v>
       </c>
-      <c r="G2" t="str">
-        <v>2025-10-06</v>
-      </c>
-      <c r="H2" t="str">
-        <v>3b2v7nwZ3t</v>
-      </c>
-      <c r="I2" t="str">
-        <v>Computers</v>
-      </c>
-      <c r="J2" t="str">
-        <v>Legacy Functionality Administrator</v>
-      </c>
-      <c r="K2" t="str">
-        <v>2024-12-12</v>
-      </c>
       <c r="L2" t="str">
-        <v>6332362254</v>
+        <v>2158121879</v>
       </c>
       <c r="M2" t="str">
-        <v>Haylee_Hilll@yahoo.com</v>
+        <v>Coralie_Becker@gmail.com</v>
       </c>
       <c r="N2" t="str">
-        <v>Concepcion</v>
+        <v>Adeline</v>
       </c>
       <c r="O2" t="str">
-        <v>22421 S Bridge Street</v>
+        <v>9832 Sporer Landing</v>
       </c>
       <c r="P2" t="str">
-        <v>73104</v>
+        <v>42793</v>
       </c>
       <c r="Q2" t="str">
-        <v>2025-02-17</v>
+        <v>2025-07-03</v>
       </c>
       <c r="R2" t="str">
-        <v>2025-03-22</v>
+        <v>2025-09-06</v>
       </c>
       <c r="S2" t="str">
-        <v>2026-05-10</v>
+        <v>2026-12-17</v>
       </c>
       <c r="T2" t="str">
-        <v>Certe apud bis tubineus addo adinventitias quo.</v>
+        <v>Tabgo aedificium tergiversatio defendo odio causa ratione atrocitas utroque.</v>
       </c>
     </row>
   </sheetData>

--- a/Encollect_Web_DBS_P1/Cypress/fixtures/AgentTemplate.xlsx
+++ b/Encollect_Web_DBS_P1/Cypress/fixtures/AgentTemplate.xlsx
@@ -404,61 +404,61 @@
         <v>123456</v>
       </c>
       <c r="B2" t="str">
-        <v>Murray</v>
+        <v>Beatty</v>
       </c>
       <c r="C2" t="str">
-        <v>VSRSWK</v>
+        <v>ANNQJJ</v>
       </c>
       <c r="D2" t="str">
-        <v>Ryan_Predovic@hotmail.com</v>
+        <v>Emory39@hotmail.com</v>
       </c>
       <c r="E2" t="str">
-        <v>4vwvuMKz</v>
+        <v>dYQWo3O9</v>
       </c>
       <c r="F2" t="str">
-        <v>2025-09-10</v>
+        <v>2025-06-14</v>
       </c>
       <c r="G2" t="str">
-        <v>2025-06-27</v>
+        <v>2025-08-07</v>
       </c>
       <c r="H2" t="str">
-        <v>FZpReDDzyW</v>
+        <v>3fx9pJRPZ3</v>
       </c>
       <c r="I2" t="str">
-        <v>Baby</v>
+        <v>Kids</v>
       </c>
       <c r="J2" t="str">
-        <v>Product Markets Consultant</v>
+        <v>Regional Communications Planner</v>
       </c>
       <c r="K2" t="str">
-        <v>2025-03-10</v>
+        <v>2025-10-07</v>
       </c>
       <c r="L2" t="str">
-        <v>2158121879</v>
+        <v>0461920073</v>
       </c>
       <c r="M2" t="str">
-        <v>Coralie_Becker@gmail.com</v>
+        <v>Leda.Kunde84@gmail.com</v>
       </c>
       <c r="N2" t="str">
-        <v>Adeline</v>
+        <v>Devyn</v>
       </c>
       <c r="O2" t="str">
-        <v>9832 Sporer Landing</v>
+        <v>9569 Kiehn Landing</v>
       </c>
       <c r="P2" t="str">
-        <v>42793</v>
+        <v>34331</v>
       </c>
       <c r="Q2" t="str">
-        <v>2025-07-03</v>
+        <v>2025-08-04</v>
       </c>
       <c r="R2" t="str">
-        <v>2025-09-06</v>
+        <v>2025-07-27</v>
       </c>
       <c r="S2" t="str">
-        <v>2026-12-17</v>
+        <v>2027-01-23</v>
       </c>
       <c r="T2" t="str">
-        <v>Tabgo aedificium tergiversatio defendo odio causa ratione atrocitas utroque.</v>
+        <v>Vinculum summa corona.</v>
       </c>
     </row>
   </sheetData>

--- a/Encollect_Web_DBS_P1/Cypress/fixtures/AgentTemplate.xlsx
+++ b/Encollect_Web_DBS_P1/Cypress/fixtures/AgentTemplate.xlsx
@@ -404,61 +404,61 @@
         <v>123456</v>
       </c>
       <c r="B2" t="str">
-        <v>Beatty</v>
+        <v>Torp</v>
       </c>
       <c r="C2" t="str">
-        <v>ANNQJJ</v>
+        <v>LID4MR</v>
       </c>
       <c r="D2" t="str">
-        <v>Emory39@hotmail.com</v>
+        <v>Stefan.Walter@hotmail.com</v>
       </c>
       <c r="E2" t="str">
-        <v>dYQWo3O9</v>
+        <v>z91IZ77E</v>
       </c>
       <c r="F2" t="str">
-        <v>2025-06-14</v>
+        <v>2026-05-28</v>
       </c>
       <c r="G2" t="str">
-        <v>2025-08-07</v>
+        <v>2026-04-12</v>
       </c>
       <c r="H2" t="str">
-        <v>3fx9pJRPZ3</v>
+        <v>xRFLh2dNtp</v>
       </c>
       <c r="I2" t="str">
-        <v>Kids</v>
+        <v>Beauty</v>
       </c>
       <c r="J2" t="str">
-        <v>Regional Communications Planner</v>
+        <v>Future Creative Associate</v>
       </c>
       <c r="K2" t="str">
-        <v>2025-10-07</v>
+        <v>2025-12-16</v>
       </c>
       <c r="L2" t="str">
-        <v>0461920073</v>
+        <v>3005507913</v>
       </c>
       <c r="M2" t="str">
-        <v>Leda.Kunde84@gmail.com</v>
+        <v>Francisco.Reichel89@yahoo.com</v>
       </c>
       <c r="N2" t="str">
-        <v>Devyn</v>
+        <v>Elsie</v>
       </c>
       <c r="O2" t="str">
-        <v>9569 Kiehn Landing</v>
+        <v>37696 Emmitt Shore</v>
       </c>
       <c r="P2" t="str">
-        <v>34331</v>
+        <v>05646</v>
       </c>
       <c r="Q2" t="str">
-        <v>2025-08-04</v>
+        <v>2026-05-16</v>
       </c>
       <c r="R2" t="str">
-        <v>2025-07-27</v>
+        <v>2026-04-08</v>
       </c>
       <c r="S2" t="str">
-        <v>2027-01-23</v>
+        <v>2026-08-20</v>
       </c>
       <c r="T2" t="str">
-        <v>Vinculum summa corona.</v>
+        <v>Urbs umquam brevis caelestis crustulum.</v>
       </c>
     </row>
   </sheetData>
